--- a/test_data/WTA/WTA Calculator - Loss Relief/WTA Calculator - Loss Relief_Test_Cases.xlsx
+++ b/test_data/WTA/WTA Calculator - Loss Relief/WTA Calculator - Loss Relief_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -628,7 +628,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>LossRelief_03</t>
+          <t>LossRelief_06</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -638,201 +638,25 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>'Source Jurisdiction' lists real countries</t>
+          <t>The live computed fields match an independent arithmetic calculation</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Opening 'Source Jurisdiction' must list real country names including Australia.</t>
+          <t>Entering Losses brought forward=1000, Tax losses in current period=500, Losses actually offset in current year=300 must live-compute: Brought forward losses available=1,000, Total Losses available=1,500, Losses available for offset=1,500, Losses available for carry forward=1,200, Total losses carried forward=1,200 - each independently recomputed in Python from the same formulas, not compared to itself.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>User is logged in.</t>
+          <t>User is logged in, Australia/2023-2024 selected, Ordinary loss relief mode.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Losses brought forward=1000, Tax losses in current period=500, Losses actually offset=300</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open Loss Relief Calculator
-2. Open 'Source Jurisdiction'
-3. Verify real countries are listed</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Opening 'Source Jurisdiction' must list real country names including Australia.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>'Source Jurisdiction' correctly lists 120 real countries.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'Source Jurisdiction' lists real countries including Australia</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>LossRelief_04</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Loss Relief</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>'Tax Year' lists real date-range options</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>After selecting a Source Jurisdiction, 'Tax Year' must list real date-range options (e.g. '01 July 2023 - 30 June 2024'), not plain year numbers.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia selected as Source Jurisdiction.</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Source: Australia</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open Loss Relief Calculator, select Australia
-2. Open 'Tax Year'
-3. Verify real date-range options are listed</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>After selecting a Source Jurisdiction, 'Tax Year' must list real date-range options (e.g. '01 July 2023 - 30 June 2024'), not plain year numbers.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>'Tax Year' correctly lists 16 real date-range options (e.g. '01 July 2026 - 30 June 2027').</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'Tax Year' lists real date-range options</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>LossRelief_05</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Loss Relief</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Ordinary loss relief mode shows all 13 expected fields</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>With Australia/01 July 2023-30 June 2024 selected and 'Ordinary loss relief' the default mode, all 13 expected field labels must be visible.</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia/2023-2024 selected.</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open Loss Relief Calculator, select Australia/2023-2024
-2. Verify all 13 Ordinary-mode field labels are visible</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>With Australia/01 July 2023-30 June 2024 selected and 'Ordinary loss relief' the default mode, all 13 expected field labels must be visible.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>All 13 expected Ordinary loss relief fields are visible.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] All 13 expected Ordinary-mode field labels are visible</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>LossRelief_06</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Loss Relief</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>The live computed fields match an independent arithmetic calculation</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Entering Losses brought forward=1000, Tax losses in current period=500, Losses actually offset in current year=300 must live-compute: Brought forward losses available=1,000, Total Losses available=1,500, Losses available for offset=1,500, Losses available for carry forward=1,200, Total losses carried forward=1,200 - each independently recomputed in Python from the same formulas, not compared to itself.</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia/2023-2024 selected, Ordinary loss relief mode.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Losses brought forward=1000, Tax losses in current period=500, Losses actually offset=300</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Loss Relief Calculator, select Australia/2023-2024
 2. Enter the 3 input amounts
@@ -840,551 +664,199 @@
 4. Verify every computed field matches</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Entering Losses brought forward=1000, Tax losses in current period=500, Losses actually offset in current year=300 must live-compute: Brought forward losses available=1,000, Total Losses available=1,500, Losses available for offset=1,500, Losses available for carry forward=1,200, Total losses carried forward=1,200 - each independently recomputed in Python from the same formulas, not compared to itself.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>All computed fields correctly matched the independent arithmetic calculation.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>[PASS] All computed fields match the independent arithmetic calculation</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>LossRelief_07</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>LossRelief_08</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>WTA Calculator - Loss Relief</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>'Losses actually offset' field shows its documented validation hint</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>The 'Losses actually offset in current year' field must show its hint text: 'Losses actually offset must not exceed Losses available for offset in current year.'</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Switching to 'Capital loss relief' shows the capital-specific fields</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Capital loss relief' must swap the Ordinary-mode fields for Capital-mode fields (e.g. 'Capital losses brought forward', 'Excess capital losses to carry forward').</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia/2023-2024 selected.</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open Loss Relief Calculator, select Australia/2023-2024
-2. Verify the hint text under 'Losses actually offset in current year' is visible</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>The 'Losses actually offset in current year' field must show its hint text: 'Losses actually offset must not exceed Losses available for offset in current year.'</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>The offset validation hint is correctly documented on the page.</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] The offset validation hint is visible</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>LossRelief_08</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Loss Relief</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Switching to 'Capital loss relief' shows the capital-specific fields</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Capital loss relief' must swap the Ordinary-mode fields for Capital-mode fields (e.g. 'Capital losses brought forward', 'Excess capital losses to carry forward').</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia/2023-2024 selected.</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Loss Relief Calculator, select Australia/2023-2024
 2. Click 'Capital loss relief'
 3. Verify the capital-specific fields are visible</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Capital loss relief' must swap the Ordinary-mode fields for Capital-mode fields (e.g. 'Capital losses brought forward', 'Excess capital losses to carry forward').</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Switching to 'Capital loss relief' correctly swapped in the capital-specific fields.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>[PASS] Capital-mode fields are visible and Ordinary-mode fields are gone</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>LossRelief_09</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>LossRelief_11</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>WTA Calculator - Loss Relief</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Capital loss relief mode shows exactly 9 fields in the expected editable pattern</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Capital loss relief mode must show exactly 9 input fields, with fields 1,2,4,6,8 editable and fields 3,5,7,9 disabled/computed (confirmed live) - including the real app quirk where fields 4 and 6 share the exact same visible label text ('Capital losses in current year'), so this is checked positionally.</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia/2023-2024 selected, Capital loss relief mode.</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Switching to 'By Entity' swaps in Corporate Group/Source Company fields</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'By Entity' must swap 'Source Jurisdiction' for 'Corporate Group' and 'Source Company' fields.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open Loss Relief Calculator, select Australia/2023-2024, switch to Capital mode
-2. Verify exactly 9 fields exist with the expected disabled/editable pattern</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Capital loss relief mode must show exactly 9 input fields, with fields 1,2,4,6,8 editable and fields 3,5,7,9 disabled/computed (confirmed live) - including the real app quirk where fields 4 and 6 share the exact same visible label text ('Capital losses in current year'), so this is checked positionally.</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Capital loss relief mode correctly shows exactly 9 fields in the expected editable pattern.</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Capital mode shows exactly 9 fields with the expected editable/disabled pattern</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>LossRelief_10</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Loss Relief</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Entering 'Capital losses brought forward' live-updates the computed offset field</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Entering 100 into 'Capital losses brought forward' (field 1, with no restriction entered) must live-update 'Capital loss brought forward available for offset against current year gains' (field 3, disabled) to 100.</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia/2023-2024 selected, Capital loss relief mode.</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Capital losses brought forward=100</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open Loss Relief Calculator, select Australia/2023-2024, switch to Capital mode
-2. Enter 100 into 'Capital losses brought forward'
-3. Verify the computed offset-available field becomes 100</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Entering 100 into 'Capital losses brought forward' (field 1, with no restriction entered) must live-update 'Capital loss brought forward available for offset against current year gains' (field 3, disabled) to 100.</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>The computed field correctly updated to 100 after entering 100.</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'Capital loss brought forward available' computes to 100</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>LossRelief_11</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Loss Relief</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Switching to 'By Entity' swaps in Corporate Group/Source Company fields</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'By Entity' must swap 'Source Jurisdiction' for 'Corporate Group' and 'Source Company' fields.</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Loss Relief Calculator
 2. Click 'By Entity'
 3. Verify 'Corporate Group' and 'Source Company' fields are visible</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Clicking 'By Entity' must swap 'Source Jurisdiction' for 'Corporate Group' and 'Source Company' fields.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Switching to 'By Entity' correctly swapped in the entity-based fields.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'By Entity' mode shows Corporate Group/Source Company fields</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>LossRelief_12</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>LossRelief_13</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>WTA Calculator - Loss Relief</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>'Corporate Group' lists this account's real entity charts</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>In 'By Entity' mode, opening 'Corporate Group' must list this account's real, previously-created entity charts.</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, 'By Entity' mode selected.</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>'Start over' shows a confirmation dialog</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Start over' must show a confirmation dialog reading 'Are you sure to reset all your selections?' with Cancel/Yes actions - the same dialog as WHT Router, not an immediate reset.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open Loss Relief Calculator, switch to 'By Entity'
-2. Open 'Corporate Group'
-3. Verify at least one real entity chart is listed</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>In 'By Entity' mode, opening 'Corporate Group' must list this account's real, previously-created entity charts.</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>'Corporate Group' correctly lists 20 real entity chart(s): ['Demo Entity Chart', 'Natmed', 'Empty', 'N', 'Empty Entity Chart', 'Copy of Demo Import Test', 'New Chart with 3rd Party', 'Testing Empty Chart', 'New AG', 'New 3423', 'new', 'testt', 'Royal Enfield Incorporation', 'Test MM', 'new v2', 'Blank', 'JHUMKAH', 'RETRS', 'chuppp', 'BEINTEHA'].</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'Corporate Group' lists at least one real entity chart</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>LossRelief_13</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Loss Relief</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>'Start over' shows a confirmation dialog</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Start over' must show a confirmation dialog reading 'Are you sure to reset all your selections?' with Cancel/Yes actions - the same dialog as WHT Router, not an immediate reset.</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Loss Relief Calculator
 2. Click 'Start over'
 3. Verify the confirmation dialog</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Start over' must show a confirmation dialog reading 'Are you sure to reset all your selections?' with Cancel/Yes actions - the same dialog as WHT Router, not an immediate reset.</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>'Start over' correctly showed a confirmation dialog before resetting.</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Start over' shows the expected confirmation dialog</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>LossRelief_14</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Loss Relief</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Confirming 'Start over' (Yes) resets the Source Jurisdiction selection</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Confirming 'Start over' with 'Yes' must reset the Source Jurisdiction select back to its 'Select' placeholder state.</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia selected as Source Jurisdiction.</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Source: Australia</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open Loss Relief Calculator, select Australia
-2. Click 'Start over' then 'Yes'
-3. Verify Source Jurisdiction resets to 'Select'</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Confirming 'Start over' with 'Yes' must reset the Source Jurisdiction select back to its 'Select' placeholder state.</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Confirming 'Start over' correctly reset the selection to its placeholder state.</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Source Jurisdiction resets to the 'Select' placeholder</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>LossRelief_15</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Loss Relief</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>'Start over' Cancel keeps the current selection</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Clicking Cancel on the Start Over confirmation must leave the already-selected Source Jurisdiction untouched.</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia selected as Source Jurisdiction.</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Source: Australia</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open Loss Relief Calculator, select Australia
-2. Click 'Start over' then Cancel
-3. Verify Source Jurisdiction is still Australia</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Clicking Cancel on the Start Over confirmation must leave the already-selected Source Jurisdiction untouched.</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Cancelling 'Start over' correctly preserved the current selection.</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Source Jurisdiction selection survives Cancel</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
